--- a/Plotting/Results_excels/production_shares_ammonia_Scope1-3.xlsx
+++ b/Plotting/Results_excels/production_shares_ammonia_Scope1-3.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1183999.999999957</v>
+        <v>1183999.999999963</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1183999.999999999</v>
+        <v>1184000.000000057</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -623,19 +623,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1179586.812507884</v>
+        <v>1179579.607275506</v>
       </c>
       <c r="G6" t="n">
-        <v>1179258.282746874</v>
+        <v>1179257.901781886</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6.209593093536825e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1179593.288345533</v>
+        <v>1179563.137326123</v>
       </c>
       <c r="J6" t="n">
-        <v>1179267.814186228</v>
+        <v>1179238.698890394</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3.642707000718108e-09</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
